--- a/calendar/Fuadijan-Monthly-Template.xlsx
+++ b/calendar/Fuadijan-Monthly-Template.xlsx
@@ -1545,13 +1545,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1575,6 +1576,11 @@
           <t>footer</t>
         </is>
       </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>preferred style</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1597,6 +1603,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1619,6 +1630,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1641,6 +1657,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1663,6 +1684,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1685,6 +1711,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1707,6 +1738,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>poster</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1729,6 +1765,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1751,6 +1792,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1773,6 +1819,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1795,6 +1846,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>invite</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1817,6 +1873,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1839,6 +1900,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1861,6 +1927,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1883,6 +1954,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>invite</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1905,6 +1981,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1927,6 +2008,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1949,6 +2035,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1971,6 +2062,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1993,6 +2089,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2015,6 +2116,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2037,6 +2143,11 @@
           <t>address</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2059,6 +2170,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2081,6 +2197,11 @@
           <t>brand</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2101,6 +2222,18 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>brand</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Styles: band (house look), split (a word above and below the dish), poster (light paper, plate in front of the headline), flat (solid Ember, plate off the bottom), invite (Night panel, photo off one side, date and hours). The art director may still choose another when the photo cannot carry it; a /redo note ("poster") locks one.</t>
         </is>
       </c>
     </row>
